--- a/docs/package/05_Delivery/Upload_Templates/Disbursements_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Disbursements_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="75">
   <si>
     <t xml:space="preserve">Voucher Date</t>
   </si>
@@ -186,12 +186,6 @@
     <t xml:space="preserve">Accounts &gt; Disbursement &gt; Bulk upload</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/disbursements/bulk-upload (multipart field "file")</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -201,7 +195,7 @@
     <t xml:space="preserve">Row limit</t>
   </si>
   <si>
-    <t xml:space="preserve">Up to 1,000 data rows per file (Configuration setting limits.bulk_upload_max_rows) and 10 MB.</t>
+    <t xml:space="preserve">Up to 1,000 data rows per file and 10 MB.</t>
   </si>
   <si>
     <t xml:space="preserve">Required columns</t>
@@ -240,10 +234,10 @@
     <t xml:space="preserve">Each row creates a draft payment voucher. Vouchers are then approved and paid on the Disbursement screen (maker-checker).</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -251,9 +245,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -280,8 +274,42 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F6B76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -309,6 +337,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -340,9 +386,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -363,6 +409,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -675,7 +728,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -778,14 +831,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/package/05_Delivery/Upload_Templates/Disbursements_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Disbursements_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="81">
   <si>
     <t xml:space="preserve">Voucher Date</t>
   </si>
@@ -48,6 +48,12 @@
     <t xml:space="preserve">Remarks</t>
   </si>
   <si>
+    <t xml:space="preserve">Refund Reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refund Note</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-10-06</t>
   </si>
   <si>
@@ -166,6 +172,18 @@
   </si>
   <si>
     <t xml:space="preserve">remarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer refund: reason code of the refund context (e.g. REF-CANCEL); required with disbursements.refund_reason_required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refundReasonCode, refundReason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note of the refund reason, when the reason asks for one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refundNote</t>
   </si>
   <si>
     <t xml:space="preserve">Item</t>
@@ -425,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -439,9 +457,11 @@
     <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="29" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="19" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20" customHeight="1">
+    <row r="1" spans="1:13" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -475,31 +495,37 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -509,7 +535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -522,22 +548,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -545,16 +571,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -562,19 +588,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -582,13 +608,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -596,16 +622,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -613,16 +639,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -630,13 +656,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -644,16 +670,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -661,16 +687,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -678,13 +704,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -692,16 +718,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -709,16 +735,44 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -737,98 +791,98 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
